--- a/Other Docs/Class list.xlsx
+++ b/Other Docs/Class list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vomit\Desktop\R Code Camp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vomit\Desktop\R-Code-Camp-CSU\Other Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9842A7A1-70EC-4D2E-947F-EB7231EC4E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1D952A-7537-4156-8527-4D6F5B8581F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>Agyemang-Duah</t>
   </si>
@@ -169,6 +169,15 @@
   </si>
   <si>
     <t>Charlie</t>
+  </si>
+  <si>
+    <t>Camden.Fahnline@colostate.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camden </t>
+  </si>
+  <si>
+    <t>Fahnline</t>
   </si>
 </sst>
 </file>
@@ -495,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:D18"/>
+  <dimension ref="A3:D19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
@@ -727,6 +736,20 @@
         <v>45</v>
       </c>
     </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
